--- a/pilot/pilot_annotator_B.xlsx
+++ b/pilot/pilot_annotator_B.xlsx
@@ -464,7 +464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Boundary judgements - pilot (Paper 2)</t>
+          <t>Boundary judgements - pilot</t>
         </is>
       </c>
     </row>
